--- a/artfynd/A 29141-2025 artfynd.xlsx
+++ b/artfynd/A 29141-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120553176</v>
+        <v>120553173</v>
       </c>
       <c r="B2" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520263</v>
+        <v>520374</v>
       </c>
       <c r="R2" t="n">
-        <v>6997919</v>
+        <v>6997890</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +767,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov bränd och ihålig tallåga</t>
+          <t>1 substratenheter # gammal tallstock</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120553184</v>
+        <v>120553176</v>
       </c>
       <c r="B3" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520125</v>
+        <v>520263</v>
       </c>
       <c r="R3" t="n">
-        <v>6997862</v>
+        <v>6997919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,7 +881,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal tallåga efter fallen brandhögstubbe</t>
+          <t>1 substratenheter # grov bränd och ihålig tallåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120553185</v>
+        <v>120553182</v>
       </c>
       <c r="B4" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520125</v>
+        <v>519989</v>
       </c>
       <c r="R4" t="n">
-        <v>6997862</v>
+        <v>6997878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +987,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>140-årig tallskog på morän med fattigris och lav</t>
+          <t>140-årig tallskog med inslag av gamla tallar på morän med fattigris och lav</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1010,7 +995,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal tallåga efter fallen brandhögstubbe</t>
+          <t>1 substratenheter # torr gammal tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,15 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120553180</v>
+        <v>120553184</v>
       </c>
       <c r="B5" t="n">
-        <v>91949</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1028,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520030</v>
+        <v>520125</v>
       </c>
       <c r="R5" t="n">
-        <v>6998006</v>
+        <v>6997862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,6 +1102,14 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>140-årig tallskog på morän med fattigris och lav</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal tallåga efter fallen brandhögstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,15 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120553177</v>
+        <v>120553188</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520125</v>
+        <v>520161</v>
       </c>
       <c r="R6" t="n">
-        <v>6997923</v>
+        <v>6997845</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1223,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal skorstenshögstubbe</t>
+          <t>1 substratenheter # grov gammal rest av vindfälle, på rotbenen</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1262,15 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120553188</v>
+        <v>120553187</v>
       </c>
       <c r="B7" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,7 +1283,7 @@
         <v>520161</v>
       </c>
       <c r="R7" t="n">
-        <v>6997845</v>
+        <v>6997850</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1337,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal rest av vindfälle, på rotbenen</t>
+          <t>1 substratenheter # grov gammal tallgren</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1381,15 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120553181</v>
+        <v>120553186</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,21 +1370,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520023</v>
+        <v>520125</v>
       </c>
       <c r="R8" t="n">
-        <v>6997999</v>
+        <v>6997862</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,7 +1451,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # rotben av mycket gammalt tallvindfälle</t>
+          <t>1 substratenheter # grov gammal tallåga efter fallen brandhögstubbe</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1500,15 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120553187</v>
+        <v>120553180</v>
       </c>
       <c r="B9" t="n">
-        <v>89735</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1540,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520161</v>
+        <v>520030</v>
       </c>
       <c r="R9" t="n">
-        <v>6997850</v>
+        <v>6998006</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,14 +1558,6 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>140-årig tallskog på morän med fattigris och lav</t>
-        </is>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal tallgren</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1619,15 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120553186</v>
+        <v>120553185</v>
       </c>
       <c r="B10" t="n">
-        <v>92152</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,21 +1590,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1731,6 +1686,574 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120553178</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ö om Sandtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>520155</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6998017</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på morän med fattigris och lav</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120553175</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ö om Sandtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>520277</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6997964</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på morän med fattigris och lav</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>1 substratenheter # tallhögstubbe med bohål</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120553177</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ö om Sandtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>520125</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6997923</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på morän med fattigris och lav</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal skorstenshögstubbe</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120553181</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ö om Sandtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>520023</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6997999</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på morän med fattigris och lav</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rotben av mycket gammalt tallvindfälle</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120553191</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ö om Sandtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>520159</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6997799</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på morän med fattigris och lav</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>under äldre tallåga mot marken</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 29141-2025 artfynd.xlsx
+++ b/artfynd/A 29141-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553173</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553176</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553182</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553184</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553188</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553187</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553186</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553180</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1690,6 +1735,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553185</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1804,6 +1854,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553178</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1918,6 +1973,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553175</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2032,6 +2092,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553177</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2146,6 +2211,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553181</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2258,8 +2328,29 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553191</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>